--- a/casad_amc_template.xlsx
+++ b/casad_amc_template.xlsx
@@ -11,11 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix-A" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix-B" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix-B 21-22" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix-C-" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GURUJI SUB - 1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GURUJI SUB - 2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GURUJI SUPER - 1" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GURUJI SUPER - 2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appendix - Photos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'TITLE PAGE'!$A$1:$G$12</definedName>
@@ -25,10 +25,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Appendix-B'!$1:$1,'Appendix-B'!$A:$B</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Appendix-B'!$A$1:$C$129</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Appendix-B 21-22'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'GURUJI SUB - 1'!$A$1:$Y$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'GURUJI SUB - 2'!$A$1:$Q$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'GURUJI SUPER - 1'!$A$1:$T$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'GURUJI SUPER - 2'!$A$1:$U$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Table 1'!$A$1:$Y$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Table 2'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Table 3'!$A$1:$T$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Table 4'!$A$1:$U$15</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2239,7 +2239,7 @@
       <c r="A2" s="50" t="n"/>
       <c r="B2" s="256" t="inlineStr">
         <is>
-          <t>Approach towards Khokara rd</t>
+          <t>Approach towards ...</t>
         </is>
       </c>
       <c r="C2" s="255" t="n"/>
@@ -2271,86 +2271,22 @@
         </is>
       </c>
       <c r="D3" s="53" t="n"/>
-      <c r="E3" s="100" t="inlineStr">
-        <is>
-          <t>P15-P16 (RW)</t>
-        </is>
-      </c>
-      <c r="F3" s="100" t="inlineStr">
-        <is>
-          <t>P16-P17</t>
-        </is>
-      </c>
-      <c r="G3" s="100" t="inlineStr">
-        <is>
-          <t>P17-P18</t>
-        </is>
-      </c>
-      <c r="H3" s="100" t="inlineStr">
-        <is>
-          <t>P18-P19</t>
-        </is>
-      </c>
-      <c r="I3" s="100" t="inlineStr">
-        <is>
-          <t>P19-P20</t>
-        </is>
-      </c>
-      <c r="J3" s="100" t="inlineStr">
-        <is>
-          <t>P20-P21</t>
-        </is>
-      </c>
-      <c r="K3" s="100" t="inlineStr">
-        <is>
-          <t>P21-P22</t>
-        </is>
-      </c>
-      <c r="L3" s="100" t="inlineStr">
-        <is>
-          <t>P22-P23</t>
-        </is>
-      </c>
-      <c r="M3" s="100" t="inlineStr">
-        <is>
-          <t>P23-P24</t>
-        </is>
-      </c>
-      <c r="N3" s="100" t="inlineStr">
-        <is>
-          <t>P24-P25</t>
-        </is>
-      </c>
-      <c r="O3" s="100" t="inlineStr">
-        <is>
-          <t>P25-P26</t>
-        </is>
-      </c>
-      <c r="P3" s="100" t="inlineStr">
-        <is>
-          <t>P26-P27</t>
-        </is>
-      </c>
-      <c r="Q3" s="100" t="inlineStr">
-        <is>
-          <t>P27-P28</t>
-        </is>
-      </c>
-      <c r="R3" s="100" t="inlineStr">
-        <is>
-          <t>P28-P29</t>
-        </is>
-      </c>
-      <c r="S3" s="100" t="inlineStr">
-        <is>
-          <t>P29-P30</t>
-        </is>
-      </c>
-      <c r="T3" s="100" t="inlineStr">
-        <is>
-          <t>P30-A2</t>
-        </is>
-      </c>
+      <c r="E3" s="100" t="n"/>
+      <c r="F3" s="100" t="n"/>
+      <c r="G3" s="100" t="n"/>
+      <c r="H3" s="100" t="n"/>
+      <c r="I3" s="100" t="n"/>
+      <c r="J3" s="100" t="n"/>
+      <c r="K3" s="100" t="n"/>
+      <c r="L3" s="100" t="n"/>
+      <c r="M3" s="100" t="n"/>
+      <c r="N3" s="100" t="n"/>
+      <c r="O3" s="100" t="n"/>
+      <c r="P3" s="100" t="n"/>
+      <c r="Q3" s="100" t="n"/>
+      <c r="R3" s="100" t="n"/>
+      <c r="S3" s="100" t="n"/>
+      <c r="T3" s="100" t="n"/>
       <c r="U3" s="56" t="inlineStr">
         <is>
           <t>Remarks/ Sketch/ Photo Ref.
@@ -2367,16 +2303,8 @@
         </is>
       </c>
       <c r="D4" s="98" t="n"/>
-      <c r="E4" s="92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RCC T-beam deck slab </t>
-        </is>
-      </c>
-      <c r="F4" s="218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RCC T-beam deck slab </t>
-        </is>
-      </c>
+      <c r="E4" s="92" t="n"/>
+      <c r="F4" s="218" t="n"/>
       <c r="G4" s="253" t="n"/>
       <c r="H4" s="253" t="n"/>
       <c r="I4" s="253" t="n"/>
@@ -2411,96 +2339,24 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E5" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G5" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H5" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="M5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O5" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T5" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="U5" s="61" t="inlineStr">
-        <is>
-          <t>1, 3, 5, 6, 9, 13</t>
-        </is>
-      </c>
-      <c r="W5" s="49" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E5" s="101" t="n"/>
+      <c r="F5" s="101" t="n"/>
+      <c r="G5" s="101" t="n"/>
+      <c r="H5" s="101" t="n"/>
+      <c r="I5" s="101" t="n"/>
+      <c r="J5" s="101" t="n"/>
+      <c r="K5" s="101" t="n"/>
+      <c r="L5" s="101" t="n"/>
+      <c r="M5" s="101" t="n"/>
+      <c r="N5" s="101" t="n"/>
+      <c r="O5" s="101" t="n"/>
+      <c r="P5" s="101" t="n"/>
+      <c r="Q5" s="101" t="n"/>
+      <c r="R5" s="101" t="n"/>
+      <c r="S5" s="101" t="n"/>
+      <c r="T5" s="101" t="n"/>
+      <c r="U5" s="61" t="n"/>
+      <c r="W5" s="49" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="60" t="n"/>
@@ -2519,96 +2375,24 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E6" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F6" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L6" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O6" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S6" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T6" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U6" s="61" t="inlineStr">
-        <is>
-          <t>4, 14</t>
-        </is>
-      </c>
-      <c r="W6" s="63" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E6" s="101" t="n"/>
+      <c r="F6" s="101" t="n"/>
+      <c r="G6" s="101" t="n"/>
+      <c r="H6" s="101" t="n"/>
+      <c r="I6" s="101" t="n"/>
+      <c r="J6" s="101" t="n"/>
+      <c r="K6" s="101" t="n"/>
+      <c r="L6" s="101" t="n"/>
+      <c r="M6" s="101" t="n"/>
+      <c r="N6" s="101" t="n"/>
+      <c r="O6" s="101" t="n"/>
+      <c r="P6" s="101" t="n"/>
+      <c r="Q6" s="101" t="n"/>
+      <c r="R6" s="101" t="n"/>
+      <c r="S6" s="101" t="n"/>
+      <c r="T6" s="101" t="n"/>
+      <c r="U6" s="61" t="n"/>
+      <c r="W6" s="63" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="51" t="n"/>
@@ -2627,96 +2411,24 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F7" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="M7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O7" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q7" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T7" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="U7" s="61" t="inlineStr">
-        <is>
-          <t>18, 1, 2, 8, 15</t>
-        </is>
-      </c>
-      <c r="W7" s="49" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
+      <c r="E7" s="101" t="n"/>
+      <c r="F7" s="101" t="n"/>
+      <c r="G7" s="101" t="n"/>
+      <c r="H7" s="101" t="n"/>
+      <c r="I7" s="101" t="n"/>
+      <c r="J7" s="101" t="n"/>
+      <c r="K7" s="101" t="n"/>
+      <c r="L7" s="101" t="n"/>
+      <c r="M7" s="101" t="n"/>
+      <c r="N7" s="101" t="n"/>
+      <c r="O7" s="101" t="n"/>
+      <c r="P7" s="101" t="n"/>
+      <c r="Q7" s="101" t="n"/>
+      <c r="R7" s="101" t="n"/>
+      <c r="S7" s="101" t="n"/>
+      <c r="T7" s="101" t="n"/>
+      <c r="U7" s="61" t="n"/>
+      <c r="W7" s="49" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="60" t="n"/>
@@ -2735,91 +2447,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="M8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T8" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="U8" s="61" t="inlineStr">
-        <is>
-          <t>19, 40, 8, 10, 11, 12, 15</t>
-        </is>
-      </c>
+      <c r="E8" s="101" t="n"/>
+      <c r="F8" s="101" t="n"/>
+      <c r="G8" s="101" t="n"/>
+      <c r="H8" s="101" t="n"/>
+      <c r="I8" s="101" t="n"/>
+      <c r="J8" s="101" t="n"/>
+      <c r="K8" s="101" t="n"/>
+      <c r="L8" s="101" t="n"/>
+      <c r="M8" s="101" t="n"/>
+      <c r="N8" s="101" t="n"/>
+      <c r="O8" s="101" t="n"/>
+      <c r="P8" s="101" t="n"/>
+      <c r="Q8" s="101" t="n"/>
+      <c r="R8" s="101" t="n"/>
+      <c r="S8" s="101" t="n"/>
+      <c r="T8" s="101" t="n"/>
+      <c r="U8" s="61" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="60" t="n"/>
@@ -2838,91 +2482,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E9" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="M9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T9" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="U9" s="61" t="inlineStr">
-        <is>
-          <t>4, 6, 14</t>
-        </is>
-      </c>
+      <c r="E9" s="101" t="n"/>
+      <c r="F9" s="101" t="n"/>
+      <c r="G9" s="101" t="n"/>
+      <c r="H9" s="101" t="n"/>
+      <c r="I9" s="101" t="n"/>
+      <c r="J9" s="101" t="n"/>
+      <c r="K9" s="101" t="n"/>
+      <c r="L9" s="101" t="n"/>
+      <c r="M9" s="101" t="n"/>
+      <c r="N9" s="101" t="n"/>
+      <c r="O9" s="101" t="n"/>
+      <c r="P9" s="101" t="n"/>
+      <c r="Q9" s="101" t="n"/>
+      <c r="R9" s="101" t="n"/>
+      <c r="S9" s="101" t="n"/>
+      <c r="T9" s="101" t="n"/>
+      <c r="U9" s="61" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="60" t="n"/>
@@ -2941,91 +2517,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="M10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P10" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T10" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U10" s="61" t="inlineStr">
-        <is>
-          <t>5, 10, 11</t>
-        </is>
-      </c>
+      <c r="E10" s="101" t="n"/>
+      <c r="F10" s="101" t="n"/>
+      <c r="G10" s="101" t="n"/>
+      <c r="H10" s="101" t="n"/>
+      <c r="I10" s="101" t="n"/>
+      <c r="J10" s="101" t="n"/>
+      <c r="K10" s="101" t="n"/>
+      <c r="L10" s="101" t="n"/>
+      <c r="M10" s="101" t="n"/>
+      <c r="N10" s="101" t="n"/>
+      <c r="O10" s="101" t="n"/>
+      <c r="P10" s="101" t="n"/>
+      <c r="Q10" s="101" t="n"/>
+      <c r="R10" s="101" t="n"/>
+      <c r="S10" s="101" t="n"/>
+      <c r="T10" s="101" t="n"/>
+      <c r="U10" s="61" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="60" t="n"/>
@@ -3044,91 +2552,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L11" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S11" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T11" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U11" s="61" t="inlineStr">
-        <is>
-          <t>5, 11, 12</t>
-        </is>
-      </c>
+      <c r="E11" s="101" t="n"/>
+      <c r="F11" s="101" t="n"/>
+      <c r="G11" s="101" t="n"/>
+      <c r="H11" s="101" t="n"/>
+      <c r="I11" s="101" t="n"/>
+      <c r="J11" s="101" t="n"/>
+      <c r="K11" s="101" t="n"/>
+      <c r="L11" s="101" t="n"/>
+      <c r="M11" s="101" t="n"/>
+      <c r="N11" s="101" t="n"/>
+      <c r="O11" s="101" t="n"/>
+      <c r="P11" s="101" t="n"/>
+      <c r="Q11" s="101" t="n"/>
+      <c r="R11" s="101" t="n"/>
+      <c r="S11" s="101" t="n"/>
+      <c r="T11" s="101" t="n"/>
+      <c r="U11" s="61" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="60" t="n"/>
@@ -3147,86 +2587,22 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E12" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L12" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="N12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S12" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T12" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E12" s="101" t="n"/>
+      <c r="F12" s="101" t="n"/>
+      <c r="G12" s="101" t="n"/>
+      <c r="H12" s="101" t="n"/>
+      <c r="I12" s="101" t="n"/>
+      <c r="J12" s="101" t="n"/>
+      <c r="K12" s="101" t="n"/>
+      <c r="L12" s="101" t="n"/>
+      <c r="M12" s="101" t="n"/>
+      <c r="N12" s="101" t="n"/>
+      <c r="O12" s="101" t="n"/>
+      <c r="P12" s="101" t="n"/>
+      <c r="Q12" s="101" t="n"/>
+      <c r="R12" s="101" t="n"/>
+      <c r="S12" s="101" t="n"/>
+      <c r="T12" s="101" t="n"/>
       <c r="U12" s="61" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -3246,91 +2622,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E13" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G13" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="K13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="L13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="M13" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N13" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O13" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T13" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="U13" s="61" t="inlineStr">
-        <is>
-          <t>5, 14</t>
-        </is>
-      </c>
+      <c r="E13" s="101" t="n"/>
+      <c r="F13" s="101" t="n"/>
+      <c r="G13" s="101" t="n"/>
+      <c r="H13" s="101" t="n"/>
+      <c r="I13" s="101" t="n"/>
+      <c r="J13" s="101" t="n"/>
+      <c r="K13" s="101" t="n"/>
+      <c r="L13" s="101" t="n"/>
+      <c r="M13" s="101" t="n"/>
+      <c r="N13" s="101" t="n"/>
+      <c r="O13" s="101" t="n"/>
+      <c r="P13" s="101" t="n"/>
+      <c r="Q13" s="101" t="n"/>
+      <c r="R13" s="101" t="n"/>
+      <c r="S13" s="101" t="n"/>
+      <c r="T13" s="101" t="n"/>
+      <c r="U13" s="61" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="60" t="n"/>
@@ -3349,86 +2657,22 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E14" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="K14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="L14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N14" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="O14" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q14" s="101" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T14" s="101" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E14" s="101" t="n"/>
+      <c r="F14" s="101" t="n"/>
+      <c r="G14" s="101" t="n"/>
+      <c r="H14" s="101" t="n"/>
+      <c r="I14" s="101" t="n"/>
+      <c r="J14" s="101" t="n"/>
+      <c r="K14" s="101" t="n"/>
+      <c r="L14" s="101" t="n"/>
+      <c r="M14" s="101" t="n"/>
+      <c r="N14" s="101" t="n"/>
+      <c r="O14" s="101" t="n"/>
+      <c r="P14" s="101" t="n"/>
+      <c r="Q14" s="101" t="n"/>
+      <c r="R14" s="101" t="n"/>
+      <c r="S14" s="101" t="n"/>
+      <c r="T14" s="101" t="n"/>
       <c r="U14" s="61" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
@@ -3452,11 +2696,7 @@
       <c r="F15" s="95" t="n"/>
       <c r="G15" s="95" t="n"/>
       <c r="H15" s="95" t="n"/>
-      <c r="I15" s="260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note :Shops are constructed below superstructure so major portion below superstructure and around  substructure not observed due to non-accesibility. Only accessible and visible portion inspected  </t>
-        </is>
-      </c>
+      <c r="I15" s="260" t="n"/>
       <c r="J15" s="261" t="n"/>
       <c r="K15" s="261" t="n"/>
       <c r="L15" s="261" t="n"/>
@@ -13059,7 +12299,7 @@
       <c r="A2" s="50" t="n"/>
       <c r="B2" s="256" t="inlineStr">
         <is>
-          <t>Approach towards Khokara rd</t>
+          <t>Approach towards ...</t>
         </is>
       </c>
       <c r="C2" s="255" t="n"/>
@@ -13095,106 +12335,26 @@
         </is>
       </c>
       <c r="D3" s="53" t="n"/>
-      <c r="E3" s="54" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="F3" s="54" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G3" s="54" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H3" s="54" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I3" s="54" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="J3" s="54" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="K3" s="54" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="L3" s="54" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="M3" s="54" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="N3" s="54" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="O3" s="54" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="P3" s="54" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="Q3" s="54" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="R3" s="54" t="inlineStr">
-        <is>
-          <t>P13 (RW)</t>
-        </is>
-      </c>
-      <c r="S3" s="54" t="inlineStr">
-        <is>
-          <t>P14 (RW)</t>
-        </is>
-      </c>
-      <c r="T3" s="54" t="inlineStr">
-        <is>
-          <t>P15 (RW)</t>
-        </is>
-      </c>
-      <c r="U3" s="54" t="inlineStr">
-        <is>
-          <t>P16 (RW)</t>
-        </is>
-      </c>
-      <c r="V3" s="54" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="W3" s="54" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="X3" s="55" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="55" t="n"/>
       <c r="Y3" s="56" t="inlineStr">
         <is>
           <t>Remarks/ Sketch/ Photo Ref.
@@ -13220,116 +12380,28 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="W4" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="X4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Y4" s="59" t="inlineStr">
-        <is>
-          <t>21, 22</t>
-        </is>
-      </c>
-      <c r="AA4" s="49" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="59" t="n"/>
+      <c r="G4" s="59" t="n"/>
+      <c r="H4" s="59" t="n"/>
+      <c r="I4" s="59" t="n"/>
+      <c r="J4" s="59" t="n"/>
+      <c r="K4" s="59" t="n"/>
+      <c r="L4" s="59" t="n"/>
+      <c r="M4" s="59" t="n"/>
+      <c r="N4" s="59" t="n"/>
+      <c r="O4" s="59" t="n"/>
+      <c r="P4" s="59" t="n"/>
+      <c r="Q4" s="59" t="n"/>
+      <c r="R4" s="59" t="n"/>
+      <c r="S4" s="59" t="n"/>
+      <c r="T4" s="59" t="n"/>
+      <c r="U4" s="59" t="n"/>
+      <c r="V4" s="59" t="n"/>
+      <c r="W4" s="59" t="n"/>
+      <c r="X4" s="59" t="n"/>
+      <c r="Y4" s="59" t="n"/>
+      <c r="AA4" s="49" t="n"/>
     </row>
     <row r="5" ht="55.5" customHeight="1">
       <c r="A5" s="60" t="n"/>
@@ -13348,112 +12420,28 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="W5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="X5" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E5" s="59" t="n"/>
+      <c r="F5" s="59" t="n"/>
+      <c r="G5" s="59" t="n"/>
+      <c r="H5" s="59" t="n"/>
+      <c r="I5" s="59" t="n"/>
+      <c r="J5" s="59" t="n"/>
+      <c r="K5" s="59" t="n"/>
+      <c r="L5" s="59" t="n"/>
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="n"/>
+      <c r="O5" s="59" t="n"/>
+      <c r="P5" s="59" t="n"/>
+      <c r="Q5" s="59" t="n"/>
+      <c r="R5" s="59" t="n"/>
+      <c r="S5" s="59" t="n"/>
+      <c r="T5" s="59" t="n"/>
+      <c r="U5" s="59" t="n"/>
+      <c r="V5" s="59" t="n"/>
+      <c r="W5" s="59" t="n"/>
+      <c r="X5" s="59" t="n"/>
       <c r="Y5" s="59" t="n"/>
-      <c r="AA5" s="63" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="AA5" s="63" t="n"/>
     </row>
     <row r="6" ht="55.5" customHeight="1">
       <c r="A6" s="51" t="n"/>
@@ -13472,114 +12460,28 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="W6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="X6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Y6" s="59" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA6" s="49" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="59" t="n"/>
+      <c r="G6" s="59" t="n"/>
+      <c r="H6" s="59" t="n"/>
+      <c r="I6" s="59" t="n"/>
+      <c r="J6" s="59" t="n"/>
+      <c r="K6" s="59" t="n"/>
+      <c r="L6" s="59" t="n"/>
+      <c r="M6" s="59" t="n"/>
+      <c r="N6" s="59" t="n"/>
+      <c r="O6" s="59" t="n"/>
+      <c r="P6" s="59" t="n"/>
+      <c r="Q6" s="59" t="n"/>
+      <c r="R6" s="59" t="n"/>
+      <c r="S6" s="59" t="n"/>
+      <c r="T6" s="59" t="n"/>
+      <c r="U6" s="59" t="n"/>
+      <c r="V6" s="59" t="n"/>
+      <c r="W6" s="59" t="n"/>
+      <c r="X6" s="59" t="n"/>
+      <c r="Y6" s="59" t="n"/>
+      <c r="AA6" s="49" t="n"/>
     </row>
     <row r="7" ht="55.5" customHeight="1">
       <c r="A7" s="60" t="n"/>
@@ -13598,109 +12500,27 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="W7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="X7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Y7" s="59" t="n">
-        <v>27</v>
-      </c>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="59" t="n"/>
+      <c r="G7" s="59" t="n"/>
+      <c r="H7" s="59" t="n"/>
+      <c r="I7" s="59" t="n"/>
+      <c r="J7" s="59" t="n"/>
+      <c r="K7" s="59" t="n"/>
+      <c r="L7" s="59" t="n"/>
+      <c r="M7" s="59" t="n"/>
+      <c r="N7" s="59" t="n"/>
+      <c r="O7" s="59" t="n"/>
+      <c r="P7" s="59" t="n"/>
+      <c r="Q7" s="59" t="n"/>
+      <c r="R7" s="59" t="n"/>
+      <c r="S7" s="59" t="n"/>
+      <c r="T7" s="59" t="n"/>
+      <c r="U7" s="59" t="n"/>
+      <c r="V7" s="59" t="n"/>
+      <c r="W7" s="59" t="n"/>
+      <c r="X7" s="59" t="n"/>
+      <c r="Y7" s="59" t="n"/>
     </row>
     <row r="8" ht="55.5" customHeight="1">
       <c r="A8" s="60" t="n"/>
@@ -13719,111 +12539,27 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="W8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="X8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Y8" s="59" t="inlineStr">
-        <is>
-          <t>24, 25, 26</t>
-        </is>
-      </c>
+      <c r="E8" s="59" t="n"/>
+      <c r="F8" s="59" t="n"/>
+      <c r="G8" s="59" t="n"/>
+      <c r="H8" s="59" t="n"/>
+      <c r="I8" s="59" t="n"/>
+      <c r="J8" s="59" t="n"/>
+      <c r="K8" s="59" t="n"/>
+      <c r="L8" s="59" t="n"/>
+      <c r="M8" s="59" t="n"/>
+      <c r="N8" s="59" t="n"/>
+      <c r="O8" s="59" t="n"/>
+      <c r="P8" s="59" t="n"/>
+      <c r="Q8" s="59" t="n"/>
+      <c r="R8" s="59" t="n"/>
+      <c r="S8" s="59" t="n"/>
+      <c r="T8" s="59" t="n"/>
+      <c r="U8" s="59" t="n"/>
+      <c r="V8" s="59" t="n"/>
+      <c r="W8" s="59" t="n"/>
+      <c r="X8" s="59" t="n"/>
+      <c r="Y8" s="59" t="n"/>
     </row>
     <row r="9" ht="55.5" customHeight="1">
       <c r="A9" s="60" t="n"/>
@@ -13842,106 +12578,26 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="W9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="X9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="59" t="n"/>
+      <c r="G9" s="59" t="n"/>
+      <c r="H9" s="59" t="n"/>
+      <c r="I9" s="59" t="n"/>
+      <c r="J9" s="59" t="n"/>
+      <c r="K9" s="59" t="n"/>
+      <c r="L9" s="59" t="n"/>
+      <c r="M9" s="59" t="n"/>
+      <c r="N9" s="59" t="n"/>
+      <c r="O9" s="59" t="n"/>
+      <c r="P9" s="59" t="n"/>
+      <c r="Q9" s="59" t="n"/>
+      <c r="R9" s="59" t="n"/>
+      <c r="S9" s="59" t="n"/>
+      <c r="T9" s="59" t="n"/>
+      <c r="U9" s="59" t="n"/>
+      <c r="V9" s="59" t="n"/>
+      <c r="W9" s="59" t="n"/>
+      <c r="X9" s="59" t="n"/>
       <c r="Y9" s="66" t="n"/>
     </row>
     <row r="10" ht="55.5" customHeight="1">
@@ -13961,106 +12617,26 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="W10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="X10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="n"/>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
+      <c r="P10" s="59" t="n"/>
+      <c r="Q10" s="59" t="n"/>
+      <c r="R10" s="59" t="n"/>
+      <c r="S10" s="59" t="n"/>
+      <c r="T10" s="59" t="n"/>
+      <c r="U10" s="59" t="n"/>
+      <c r="V10" s="59" t="n"/>
+      <c r="W10" s="59" t="n"/>
+      <c r="X10" s="59" t="n"/>
       <c r="Y10" s="66" t="n"/>
     </row>
     <row r="11" ht="55.5" customHeight="1">
@@ -14080,106 +12656,26 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="U11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="V11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="W11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="X11" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="59" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
+      <c r="I11" s="59" t="n"/>
+      <c r="J11" s="59" t="n"/>
+      <c r="K11" s="59" t="n"/>
+      <c r="L11" s="59" t="n"/>
+      <c r="M11" s="59" t="n"/>
+      <c r="N11" s="59" t="n"/>
+      <c r="O11" s="59" t="n"/>
+      <c r="P11" s="59" t="n"/>
+      <c r="Q11" s="59" t="n"/>
+      <c r="R11" s="59" t="n"/>
+      <c r="S11" s="59" t="n"/>
+      <c r="T11" s="59" t="n"/>
+      <c r="U11" s="59" t="n"/>
+      <c r="V11" s="59" t="n"/>
+      <c r="W11" s="59" t="n"/>
+      <c r="X11" s="59" t="n"/>
       <c r="Y11" s="60" t="n"/>
     </row>
     <row r="12" ht="55.5" customHeight="1">
@@ -14199,106 +12695,26 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="W12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="X12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="59" t="n"/>
+      <c r="G12" s="59" t="n"/>
+      <c r="H12" s="59" t="n"/>
+      <c r="I12" s="59" t="n"/>
+      <c r="J12" s="59" t="n"/>
+      <c r="K12" s="59" t="n"/>
+      <c r="L12" s="59" t="n"/>
+      <c r="M12" s="59" t="n"/>
+      <c r="N12" s="59" t="n"/>
+      <c r="O12" s="59" t="n"/>
+      <c r="P12" s="59" t="n"/>
+      <c r="Q12" s="59" t="n"/>
+      <c r="R12" s="59" t="n"/>
+      <c r="S12" s="59" t="n"/>
+      <c r="T12" s="59" t="n"/>
+      <c r="U12" s="59" t="n"/>
+      <c r="V12" s="59" t="n"/>
+      <c r="W12" s="59" t="n"/>
+      <c r="X12" s="59" t="n"/>
       <c r="Y12" s="60" t="n"/>
     </row>
     <row r="13" ht="55.5" customHeight="1">
@@ -14318,106 +12734,26 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q13" s="91" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="R13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="U13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="V13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="W13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="X13" s="91" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E13" s="91" t="n"/>
+      <c r="F13" s="91" t="n"/>
+      <c r="G13" s="91" t="n"/>
+      <c r="H13" s="91" t="n"/>
+      <c r="I13" s="91" t="n"/>
+      <c r="J13" s="91" t="n"/>
+      <c r="K13" s="91" t="n"/>
+      <c r="L13" s="91" t="n"/>
+      <c r="M13" s="91" t="n"/>
+      <c r="N13" s="91" t="n"/>
+      <c r="O13" s="91" t="n"/>
+      <c r="P13" s="91" t="n"/>
+      <c r="Q13" s="91" t="n"/>
+      <c r="R13" s="91" t="n"/>
+      <c r="S13" s="91" t="n"/>
+      <c r="T13" s="91" t="n"/>
+      <c r="U13" s="91" t="n"/>
+      <c r="V13" s="91" t="n"/>
+      <c r="W13" s="91" t="n"/>
+      <c r="X13" s="91" t="n"/>
       <c r="Y13" s="94" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
@@ -14437,11 +12773,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E14" s="210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note :Shops are constructed below superstructure so major portion below superstructure and around  substructure not observed due to non-accesibility. </t>
-        </is>
-      </c>
+      <c r="E14" s="210" t="n"/>
       <c r="F14" s="253" t="n"/>
       <c r="G14" s="253" t="n"/>
       <c r="H14" s="253" t="n"/>
@@ -14456,22 +12788,10 @@
       <c r="Q14" s="241" t="n"/>
       <c r="R14" s="92" t="n"/>
       <c r="S14" s="92" t="n"/>
-      <c r="T14" s="131" t="inlineStr">
-        <is>
-          <t>Drainage pipe Damage</t>
-        </is>
-      </c>
+      <c r="T14" s="131" t="n"/>
       <c r="U14" s="92" t="n"/>
-      <c r="V14" s="130" t="inlineStr">
-        <is>
-          <t>Pier Protection work Damage</t>
-        </is>
-      </c>
-      <c r="W14" s="130" t="inlineStr">
-        <is>
-          <t>Pier Protection work Damage</t>
-        </is>
-      </c>
+      <c r="V14" s="130" t="n"/>
+      <c r="W14" s="130" t="n"/>
       <c r="X14" s="92" t="n"/>
       <c r="Y14" s="96" t="n"/>
     </row>
@@ -14497,7 +12817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="3.5703125" customWidth="1" style="49" min="1" max="1"/>
@@ -14541,7 +12861,7 @@
       <c r="A2" s="50" t="n"/>
       <c r="B2" s="256" t="inlineStr">
         <is>
-          <t>Approach towards Late Shree Jivandas Mandangopal Damani Chock</t>
+          <t>Approach towards ...</t>
         </is>
       </c>
       <c r="C2" s="255" t="n"/>
@@ -14569,67 +12889,20 @@
         </is>
       </c>
       <c r="D3" s="53" t="n"/>
-      <c r="E3" s="54" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="F3" s="54" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="G3" s="54" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="H3" s="54" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="I3" s="54" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="J3" s="54" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="K3" s="54" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="L3" s="54" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="M3" s="54" t="inlineStr">
-        <is>
-          <t>P28</t>
-        </is>
-      </c>
-      <c r="N3" s="54" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="O3" s="54" t="inlineStr">
-        <is>
-          <t>P30</t>
-        </is>
-      </c>
-      <c r="P3" s="54" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="Q3" s="56" t="inlineStr">
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="56" t="n"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Remarks/ Sketch/ Photo Ref.
 No.</t>
@@ -14654,76 +12927,20 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I4" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N4" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O4" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P4" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="Q4" s="59" t="inlineStr">
-        <is>
-          <t>28, 29, 30</t>
-        </is>
-      </c>
-      <c r="S4" s="49" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="59" t="n"/>
+      <c r="G4" s="59" t="n"/>
+      <c r="H4" s="59" t="n"/>
+      <c r="I4" s="59" t="n"/>
+      <c r="J4" s="59" t="n"/>
+      <c r="K4" s="59" t="n"/>
+      <c r="L4" s="59" t="n"/>
+      <c r="M4" s="59" t="n"/>
+      <c r="N4" s="59" t="n"/>
+      <c r="O4" s="59" t="n"/>
+      <c r="P4" s="59" t="n"/>
+      <c r="Q4" s="59" t="n"/>
+      <c r="S4" s="49" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="60" t="n"/>
@@ -14742,72 +12959,20 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O5" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E5" s="59" t="n"/>
+      <c r="F5" s="59" t="n"/>
+      <c r="G5" s="59" t="n"/>
+      <c r="H5" s="59" t="n"/>
+      <c r="I5" s="59" t="n"/>
+      <c r="J5" s="59" t="n"/>
+      <c r="K5" s="59" t="n"/>
+      <c r="L5" s="59" t="n"/>
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="n"/>
+      <c r="O5" s="59" t="n"/>
+      <c r="P5" s="59" t="n"/>
       <c r="Q5" s="61" t="n"/>
-      <c r="S5" s="63" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="S5" s="63" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="51" t="n"/>
@@ -14826,74 +12991,20 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q6" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="S6" s="49" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="59" t="n"/>
+      <c r="G6" s="59" t="n"/>
+      <c r="H6" s="59" t="n"/>
+      <c r="I6" s="59" t="n"/>
+      <c r="J6" s="59" t="n"/>
+      <c r="K6" s="59" t="n"/>
+      <c r="L6" s="59" t="n"/>
+      <c r="M6" s="59" t="n"/>
+      <c r="N6" s="59" t="n"/>
+      <c r="O6" s="59" t="n"/>
+      <c r="P6" s="59" t="n"/>
+      <c r="Q6" s="59" t="n"/>
+      <c r="S6" s="49" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="60" t="n"/>
@@ -14912,66 +13023,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="59" t="n"/>
+      <c r="G7" s="59" t="n"/>
+      <c r="H7" s="59" t="n"/>
+      <c r="I7" s="59" t="n"/>
+      <c r="J7" s="59" t="n"/>
+      <c r="K7" s="59" t="n"/>
+      <c r="L7" s="59" t="n"/>
+      <c r="M7" s="59" t="n"/>
+      <c r="N7" s="59" t="n"/>
+      <c r="O7" s="59" t="n"/>
+      <c r="P7" s="59" t="n"/>
       <c r="Q7" s="64" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
@@ -14991,66 +13054,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="G8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="I8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="J8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E8" s="59" t="n"/>
+      <c r="F8" s="59" t="n"/>
+      <c r="G8" s="59" t="n"/>
+      <c r="H8" s="59" t="n"/>
+      <c r="I8" s="59" t="n"/>
+      <c r="J8" s="59" t="n"/>
+      <c r="K8" s="59" t="n"/>
+      <c r="L8" s="59" t="n"/>
+      <c r="M8" s="59" t="n"/>
+      <c r="N8" s="59" t="n"/>
+      <c r="O8" s="59" t="n"/>
+      <c r="P8" s="59" t="n"/>
       <c r="Q8" s="66" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -15070,66 +13085,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O9" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P9" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="59" t="n"/>
+      <c r="G9" s="59" t="n"/>
+      <c r="H9" s="59" t="n"/>
+      <c r="I9" s="59" t="n"/>
+      <c r="J9" s="59" t="n"/>
+      <c r="K9" s="59" t="n"/>
+      <c r="L9" s="59" t="n"/>
+      <c r="M9" s="59" t="n"/>
+      <c r="N9" s="59" t="n"/>
+      <c r="O9" s="59" t="n"/>
+      <c r="P9" s="59" t="n"/>
       <c r="Q9" s="66" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -15149,66 +13116,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O10" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="P10" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="n"/>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
+      <c r="P10" s="59" t="n"/>
       <c r="Q10" s="66" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -15228,66 +13147,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="59" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
+      <c r="I11" s="59" t="n"/>
+      <c r="J11" s="59" t="n"/>
+      <c r="K11" s="59" t="n"/>
+      <c r="L11" s="59" t="n"/>
+      <c r="M11" s="59" t="n"/>
+      <c r="N11" s="59" t="n"/>
+      <c r="O11" s="59" t="n"/>
+      <c r="P11" s="59" t="n"/>
       <c r="Q11" s="60" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
@@ -15307,66 +13178,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="F12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G12" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="H12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="59" t="n"/>
+      <c r="G12" s="59" t="n"/>
+      <c r="H12" s="59" t="n"/>
+      <c r="I12" s="59" t="n"/>
+      <c r="J12" s="59" t="n"/>
+      <c r="K12" s="59" t="n"/>
+      <c r="L12" s="59" t="n"/>
+      <c r="M12" s="59" t="n"/>
+      <c r="N12" s="59" t="n"/>
+      <c r="O12" s="59" t="n"/>
+      <c r="P12" s="59" t="n"/>
       <c r="Q12" s="60" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -15386,66 +13209,18 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="59" t="n"/>
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="59" t="n"/>
+      <c r="I13" s="59" t="n"/>
+      <c r="J13" s="59" t="n"/>
+      <c r="K13" s="59" t="n"/>
+      <c r="L13" s="59" t="n"/>
+      <c r="M13" s="59" t="n"/>
+      <c r="N13" s="59" t="n"/>
+      <c r="O13" s="59" t="n"/>
+      <c r="P13" s="59" t="n"/>
       <c r="Q13" s="60" t="n"/>
     </row>
     <row r="14" ht="57" customHeight="1">
@@ -15465,20 +13240,12 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E14" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note :Shops are constructed below superstructure so major portion below superstructure and around  substructure not observed due to non-accesibility. Only accessible and visible portion inspected  </t>
-        </is>
-      </c>
+      <c r="E14" s="257" t="n"/>
       <c r="F14" s="255" t="n"/>
       <c r="G14" s="255" t="n"/>
       <c r="H14" s="255" t="n"/>
       <c r="I14" s="258" t="n"/>
-      <c r="J14" s="259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note :Shops are constructed below superstructure so major portion below superstructure and around  substructure not observed due to non-accesibility. </t>
-        </is>
-      </c>
+      <c r="J14" s="259" t="n"/>
       <c r="K14" s="255" t="n"/>
       <c r="L14" s="255" t="n"/>
       <c r="M14" s="255" t="n"/>
@@ -15557,7 +13324,7 @@
       <c r="A2" s="50" t="n"/>
       <c r="B2" s="256" t="inlineStr">
         <is>
-          <t>Approach towards Khokara rd</t>
+          <t>Approach towards ...</t>
         </is>
       </c>
       <c r="C2" s="255" t="n"/>
@@ -15588,81 +13355,21 @@
         </is>
       </c>
       <c r="D3" s="53" t="n"/>
-      <c r="E3" s="54" t="inlineStr">
-        <is>
-          <t>A1-P1</t>
-        </is>
-      </c>
-      <c r="F3" s="54" t="inlineStr">
-        <is>
-          <t>P1-P2</t>
-        </is>
-      </c>
-      <c r="G3" s="54" t="inlineStr">
-        <is>
-          <t>P2-P3</t>
-        </is>
-      </c>
-      <c r="H3" s="54" t="inlineStr">
-        <is>
-          <t>P3-P4</t>
-        </is>
-      </c>
-      <c r="I3" s="54" t="inlineStr">
-        <is>
-          <t>P4-P5</t>
-        </is>
-      </c>
-      <c r="J3" s="54" t="inlineStr">
-        <is>
-          <t>P5-P6</t>
-        </is>
-      </c>
-      <c r="K3" s="54" t="inlineStr">
-        <is>
-          <t>P6-P7</t>
-        </is>
-      </c>
-      <c r="L3" s="54" t="inlineStr">
-        <is>
-          <t>P7-P8</t>
-        </is>
-      </c>
-      <c r="M3" s="54" t="inlineStr">
-        <is>
-          <t>P8-P9</t>
-        </is>
-      </c>
-      <c r="N3" s="54" t="inlineStr">
-        <is>
-          <t>P9-P10</t>
-        </is>
-      </c>
-      <c r="O3" s="54" t="inlineStr">
-        <is>
-          <t>P10-P11</t>
-        </is>
-      </c>
-      <c r="P3" s="54" t="inlineStr">
-        <is>
-          <t>P11-P12</t>
-        </is>
-      </c>
-      <c r="Q3" s="54" t="inlineStr">
-        <is>
-          <t>P12-P13</t>
-        </is>
-      </c>
-      <c r="R3" s="54" t="inlineStr">
-        <is>
-          <t>P13-P14 (RW)</t>
-        </is>
-      </c>
-      <c r="S3" s="54" t="inlineStr">
-        <is>
-          <t>P14-P15 (RW)</t>
-        </is>
-      </c>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
       <c r="T3" s="56" t="inlineStr">
         <is>
           <t>Remarks/ Sketch/ Photo Ref.
@@ -15679,11 +13386,7 @@
         </is>
       </c>
       <c r="D4" s="53" t="n"/>
-      <c r="E4" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RCC T-beam deck slab </t>
-        </is>
-      </c>
+      <c r="E4" s="54" t="n"/>
       <c r="F4" s="255" t="n"/>
       <c r="G4" s="255" t="n"/>
       <c r="H4" s="255" t="n"/>
@@ -15696,11 +13399,7 @@
       <c r="O4" s="255" t="n"/>
       <c r="P4" s="255" t="n"/>
       <c r="Q4" s="235" t="n"/>
-      <c r="R4" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RCC T-beam deck slab </t>
-        </is>
-      </c>
+      <c r="R4" s="54" t="n"/>
       <c r="S4" s="235" t="n"/>
       <c r="T4" s="56" t="n"/>
     </row>
@@ -15722,87 +13421,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P5" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S5" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E5" s="59" t="n"/>
+      <c r="F5" s="59" t="n"/>
+      <c r="G5" s="59" t="n"/>
+      <c r="H5" s="59" t="n"/>
+      <c r="I5" s="59" t="n"/>
+      <c r="J5" s="59" t="n"/>
+      <c r="K5" s="59" t="n"/>
+      <c r="L5" s="59" t="n"/>
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="n"/>
+      <c r="O5" s="59" t="n"/>
+      <c r="P5" s="59" t="n"/>
+      <c r="Q5" s="59" t="n"/>
+      <c r="R5" s="59" t="n"/>
+      <c r="S5" s="59" t="n"/>
       <c r="T5" s="61" t="n"/>
-      <c r="V5" s="49" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="V5" s="49" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="60" t="n"/>
@@ -15821,89 +13456,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P6" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q6" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S6" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T6" s="61" t="n">
-        <v>4</v>
-      </c>
-      <c r="V6" s="63" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="59" t="n"/>
+      <c r="G6" s="59" t="n"/>
+      <c r="H6" s="59" t="n"/>
+      <c r="I6" s="59" t="n"/>
+      <c r="J6" s="59" t="n"/>
+      <c r="K6" s="59" t="n"/>
+      <c r="L6" s="59" t="n"/>
+      <c r="M6" s="59" t="n"/>
+      <c r="N6" s="59" t="n"/>
+      <c r="O6" s="59" t="n"/>
+      <c r="P6" s="59" t="n"/>
+      <c r="Q6" s="59" t="n"/>
+      <c r="R6" s="59" t="n"/>
+      <c r="S6" s="59" t="n"/>
+      <c r="T6" s="61" t="n"/>
+      <c r="V6" s="63" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="51" t="n"/>
@@ -15922,89 +13491,23 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P7" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R7" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S7" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="T7" s="61" t="n">
-        <v>18</v>
-      </c>
-      <c r="V7" s="49" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="59" t="n"/>
+      <c r="G7" s="59" t="n"/>
+      <c r="H7" s="59" t="n"/>
+      <c r="I7" s="59" t="n"/>
+      <c r="J7" s="59" t="n"/>
+      <c r="K7" s="59" t="n"/>
+      <c r="L7" s="59" t="n"/>
+      <c r="M7" s="59" t="n"/>
+      <c r="N7" s="59" t="n"/>
+      <c r="O7" s="59" t="n"/>
+      <c r="P7" s="59" t="n"/>
+      <c r="Q7" s="59" t="n"/>
+      <c r="R7" s="59" t="n"/>
+      <c r="S7" s="59" t="n"/>
+      <c r="T7" s="61" t="n"/>
+      <c r="V7" s="49" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="60" t="n"/>
@@ -16023,84 +13526,22 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P8" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R8" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S8" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T8" s="61" t="n">
-        <v>16</v>
-      </c>
+      <c r="E8" s="59" t="n"/>
+      <c r="F8" s="59" t="n"/>
+      <c r="G8" s="59" t="n"/>
+      <c r="H8" s="59" t="n"/>
+      <c r="I8" s="59" t="n"/>
+      <c r="J8" s="59" t="n"/>
+      <c r="K8" s="59" t="n"/>
+      <c r="L8" s="59" t="n"/>
+      <c r="M8" s="59" t="n"/>
+      <c r="N8" s="59" t="n"/>
+      <c r="O8" s="59" t="n"/>
+      <c r="P8" s="59" t="n"/>
+      <c r="Q8" s="59" t="n"/>
+      <c r="R8" s="59" t="n"/>
+      <c r="S8" s="59" t="n"/>
+      <c r="T8" s="61" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="60" t="n"/>
@@ -16119,81 +13560,21 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P9" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q9" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="R9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S9" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="59" t="n"/>
+      <c r="G9" s="59" t="n"/>
+      <c r="H9" s="59" t="n"/>
+      <c r="I9" s="59" t="n"/>
+      <c r="J9" s="59" t="n"/>
+      <c r="K9" s="59" t="n"/>
+      <c r="L9" s="59" t="n"/>
+      <c r="M9" s="59" t="n"/>
+      <c r="N9" s="59" t="n"/>
+      <c r="O9" s="59" t="n"/>
+      <c r="P9" s="59" t="n"/>
+      <c r="Q9" s="59" t="n"/>
+      <c r="R9" s="59" t="n"/>
+      <c r="S9" s="59" t="n"/>
       <c r="T9" s="61" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -16213,84 +13594,22 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P10" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R10" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S10" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T10" s="61" t="n">
-        <v>16</v>
-      </c>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="n"/>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
+      <c r="P10" s="59" t="n"/>
+      <c r="Q10" s="59" t="n"/>
+      <c r="R10" s="59" t="n"/>
+      <c r="S10" s="59" t="n"/>
+      <c r="T10" s="61" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="60" t="n"/>
@@ -16309,81 +13628,21 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P11" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S11" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="59" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
+      <c r="I11" s="59" t="n"/>
+      <c r="J11" s="59" t="n"/>
+      <c r="K11" s="59" t="n"/>
+      <c r="L11" s="59" t="n"/>
+      <c r="M11" s="59" t="n"/>
+      <c r="N11" s="59" t="n"/>
+      <c r="O11" s="59" t="n"/>
+      <c r="P11" s="59" t="n"/>
+      <c r="Q11" s="59" t="n"/>
+      <c r="R11" s="59" t="n"/>
+      <c r="S11" s="59" t="n"/>
       <c r="T11" s="61" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
@@ -16403,81 +13662,21 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P12" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R12" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="S12" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="59" t="n"/>
+      <c r="G12" s="59" t="n"/>
+      <c r="H12" s="59" t="n"/>
+      <c r="I12" s="59" t="n"/>
+      <c r="J12" s="59" t="n"/>
+      <c r="K12" s="59" t="n"/>
+      <c r="L12" s="59" t="n"/>
+      <c r="M12" s="59" t="n"/>
+      <c r="N12" s="59" t="n"/>
+      <c r="O12" s="59" t="n"/>
+      <c r="P12" s="59" t="n"/>
+      <c r="Q12" s="59" t="n"/>
+      <c r="R12" s="59" t="n"/>
+      <c r="S12" s="59" t="n"/>
       <c r="T12" s="61" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -16497,84 +13696,22 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P13" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R13" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S13" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T13" s="61" t="n">
-        <v>17</v>
-      </c>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="59" t="n"/>
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="59" t="n"/>
+      <c r="I13" s="59" t="n"/>
+      <c r="J13" s="59" t="n"/>
+      <c r="K13" s="59" t="n"/>
+      <c r="L13" s="59" t="n"/>
+      <c r="M13" s="59" t="n"/>
+      <c r="N13" s="59" t="n"/>
+      <c r="O13" s="59" t="n"/>
+      <c r="P13" s="59" t="n"/>
+      <c r="Q13" s="59" t="n"/>
+      <c r="R13" s="59" t="n"/>
+      <c r="S13" s="59" t="n"/>
+      <c r="T13" s="61" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="60" t="n"/>
@@ -16593,84 +13730,22 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="F14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="G14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="H14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="I14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="J14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="K14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="L14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="M14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="N14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="O14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="P14" s="59" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
-      <c r="Q14" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R14" s="59" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="S14" s="59" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="T14" s="61" t="n">
-        <v>20</v>
-      </c>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="59" t="n"/>
+      <c r="G14" s="59" t="n"/>
+      <c r="H14" s="59" t="n"/>
+      <c r="I14" s="59" t="n"/>
+      <c r="J14" s="59" t="n"/>
+      <c r="K14" s="59" t="n"/>
+      <c r="L14" s="59" t="n"/>
+      <c r="M14" s="59" t="n"/>
+      <c r="N14" s="59" t="n"/>
+      <c r="O14" s="59" t="n"/>
+      <c r="P14" s="59" t="n"/>
+      <c r="Q14" s="59" t="n"/>
+      <c r="R14" s="59" t="n"/>
+      <c r="S14" s="59" t="n"/>
+      <c r="T14" s="61" t="n"/>
     </row>
     <row r="15" ht="57" customHeight="1">
       <c r="A15" s="51" t="n"/>
@@ -16689,11 +13764,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="E15" s="210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note :Shops are constructed below superstructure so major portion below superstructure and around  substructure not observed due to non-accesibility. </t>
-        </is>
-      </c>
+      <c r="E15" s="210" t="n"/>
       <c r="F15" s="253" t="n"/>
       <c r="G15" s="253" t="n"/>
       <c r="H15" s="253" t="n"/>

--- a/casad_amc_template.xlsx
+++ b/casad_amc_template.xlsx
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D57" s="241" t="n"/>
     </row>
-    <row r="58" ht="38.25" customFormat="1" customHeight="1" s="4">
+    <row r="58" ht="38.25" customHeight="1">
       <c r="A58" s="246" t="n"/>
       <c r="B58" s="127" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="D83" s="241" t="n"/>
     </row>
-    <row r="84" ht="51" customFormat="1" customHeight="1" s="5">
+    <row r="84" ht="51" customHeight="1">
       <c r="A84" s="162" t="inlineStr">
         <is>
           <t>(e)</t>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="D91" s="241" t="n"/>
     </row>
-    <row r="92" ht="39.75" customFormat="1" customHeight="1" s="5">
+    <row r="92" ht="39.75" customHeight="1">
       <c r="A92" s="124" t="n">
         <v>8</v>
       </c>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D92" s="241" t="n"/>
     </row>
-    <row r="93" ht="24" customFormat="1" customHeight="1" s="5">
+    <row r="93" ht="24" customHeight="1">
       <c r="A93" s="124" t="n">
         <v>9</v>
       </c>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="D93" s="241" t="n"/>
     </row>
-    <row r="94" ht="25.5" customFormat="1" customHeight="1" s="5">
+    <row r="94" ht="25.5" customHeight="1">
       <c r="A94" s="124" t="n">
         <v>10</v>
       </c>

--- a/casad_amc_template.xlsx
+++ b/casad_amc_template.xlsx
@@ -3442,11 +3442,6 @@
           <t xml:space="preserve">Data Not Available </t>
         </is>
       </c>
-      <c r="D33" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data Not Available </t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="162" t="inlineStr">
@@ -3464,11 +3459,6 @@
           <t xml:space="preserve">Not Available </t>
         </is>
       </c>
-      <c r="D34" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Available </t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="162" t="inlineStr">
@@ -3486,11 +3476,6 @@
           <t xml:space="preserve">Not Available </t>
         </is>
       </c>
-      <c r="D35" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Available </t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="162" t="inlineStr">
@@ -3508,11 +3493,6 @@
           <t xml:space="preserve">Not Available </t>
         </is>
       </c>
-      <c r="D36" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Available </t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="162" t="inlineStr">
@@ -3530,11 +3510,6 @@
           <t xml:space="preserve">Not Available </t>
         </is>
       </c>
-      <c r="D37" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Available </t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="162" t="inlineStr">
@@ -3552,11 +3527,6 @@
           <t xml:space="preserve">Not Available </t>
         </is>
       </c>
-      <c r="D38" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Available </t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="162" t="inlineStr">
@@ -3570,11 +3540,6 @@
         </is>
       </c>
       <c r="C39" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Available </t>
-        </is>
-      </c>
-      <c r="D39" s="103" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Available </t>
         </is>
@@ -4579,7 +4544,7 @@
       <c r="D109" s="111" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="97">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C15:D15"/>
@@ -4670,6 +4635,13 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C78:D78"/>
     <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7086614173228347" right="0.4724409448818898" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
